--- a/BOND_EQT/SPX_processed.xlsx
+++ b/BOND_EQT/SPX_processed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5545"/>
+  <dimension ref="A1:B5549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44796,6 +44796,38 @@
         <v>5738.52</v>
       </c>
     </row>
+    <row r="5546">
+      <c r="A5546" s="2" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B5546" t="n">
+        <v>5770.2</v>
+      </c>
+    </row>
+    <row r="5547">
+      <c r="A5547" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B5547" t="n">
+        <v>5770.2</v>
+      </c>
+    </row>
+    <row r="5548">
+      <c r="A5548" s="2" t="n">
+        <v>45725</v>
+      </c>
+      <c r="B5548" t="n">
+        <v>5770.2</v>
+      </c>
+    </row>
+    <row r="5549">
+      <c r="A5549" s="2" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B5549" t="n">
+        <v>5770.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
